--- a/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Additional-Description-inputs.xlsx
+++ b/Full-LC-AUTO/dist/release/Full-LC-AUTO/data inputs/jeans/Additional-Description-inputs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ESHAAN\HAKUR\work--fk-tools\Full-LC-AUTO\data inputs\jeans\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1034DA12-EE68-4610-94C9-195577C74695}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88853926-87EE-413F-880F-6E09BEE0D3F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="80">
   <si>
     <t>kind</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>beige baggy jeans, beige loose fit jeans, beige relaxed fit jeans, beige wide leg jeans, beige denim jeans, khaki baggy jeans, sand color jeans, cream baggy jeans, camel jeans for men, beige oversized jeans, beige casual jeans, beige streetwear jeans, beige straight fit jeans, beige cotton denim, beige fashion jeans, men beige jeans, beige baggy fit jeans</t>
+  </si>
+  <si>
+    <t>White-baggy</t>
+  </si>
+  <si>
+    <t>White baggy jeans, White loose-fit jeans, White relaxed-fit jeans, White wide-leg jeans, White denim jeans, White oversized jeans, White casual jeans, White streetwear jeans, White straight-fit jeans, White cotton denim jeans, White fashion jeans, White jeans for men, White baggy-fit jeans, White utility jeans, White urban jeans, White everyday jeans, White hip-hop jeans, White ankle-length jeans, White roomy-fit jeans, White contemporary jeans</t>
   </si>
 </sst>
 </file>
@@ -603,7 +609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="14" customWidth="1"/>
@@ -987,6 +993,65 @@
         <v>71</v>
       </c>
     </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B7">
+        <v>28</v>
+      </c>
+      <c r="C7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
